--- a/data/trans_dic/P15D$consultar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 28,62</t>
+          <t>3,53; 31,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 17,81</t>
+          <t>3,99; 18,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 34,32</t>
+          <t>11,96; 35,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 28,94</t>
+          <t>7,27; 27,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,95</t>
+          <t>2,6; 21,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,44</t>
+          <t>4,45; 14,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 23,4</t>
+          <t>7,07; 24,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 26,38</t>
+          <t>13,73; 26,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,98</t>
+          <t>4,47; 19,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,77</t>
+          <t>5,11; 13,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 24,74</t>
+          <t>10,88; 25,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 24,33</t>
+          <t>12,75; 24,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 22,49</t>
+          <t>6,96; 23,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,87</t>
+          <t>3,23; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 16,55</t>
+          <t>5,57; 16,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,01</t>
+          <t>3,76; 15,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 36,33</t>
+          <t>8,48; 37,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 15,51</t>
+          <t>4,22; 15,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,64</t>
+          <t>3,51; 15,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 23,95</t>
+          <t>9,97; 24,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 23,63</t>
+          <t>9,07; 23,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,62</t>
+          <t>4,57; 10,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,06</t>
+          <t>6,03; 13,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 16,79</t>
+          <t>7,79; 16,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 36,53</t>
+          <t>4,21; 36,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 39,87</t>
+          <t>7,36; 38,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,52</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,08</t>
+          <t>0,0; 17,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,31</t>
+          <t>0,0; 31,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,77</t>
+          <t>3,01; 25,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,25</t>
+          <t>0,0; 18,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 41,04</t>
+          <t>15,51; 41,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 26,49</t>
+          <t>2,85; 27,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 25,55</t>
+          <t>6,76; 27,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,21</t>
+          <t>1,57; 14,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 24,34</t>
+          <t>8,51; 24,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,55</t>
+          <t>8,14; 20,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,15</t>
+          <t>5,47; 12,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 17,92</t>
+          <t>8,44; 16,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 14,0</t>
+          <t>4,91; 13,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,56</t>
+          <t>7,27; 21,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,97</t>
+          <t>5,32; 12,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,18</t>
+          <t>6,63; 15,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,78</t>
+          <t>14,63; 23,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,71</t>
+          <t>8,86; 18,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,29</t>
+          <t>6,09; 11,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,63</t>
+          <t>8,38; 14,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 17,49</t>
+          <t>11,01; 17,37</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>920; 7204</t>
+          <t>888; 7969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2981; 13326</t>
+          <t>2987; 13926</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5300; 15686</t>
+          <t>5467; 16158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2523; 10303</t>
+          <t>2588; 9847</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1183; 10448</t>
+          <t>1182; 9960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4610; 16150</t>
+          <t>4982; 16267</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5380; 17459</t>
+          <t>5274; 18041</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10519; 20990</t>
+          <t>10922; 21241</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3174; 14128</t>
+          <t>3159; 13785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8899; 23839</t>
+          <t>9538; 25036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12477; 29768</t>
+          <t>13092; 30159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15337; 28021</t>
+          <t>14679; 27939</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5350; 17653</t>
+          <t>5465; 18420</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6325; 19781</t>
+          <t>5870; 19641</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6826; 20053</t>
+          <t>6752; 20378</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4781; 20825</t>
+          <t>4885; 20752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2746; 12732</t>
+          <t>2970; 13163</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4997; 17639</t>
+          <t>4793; 17446</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2950; 13243</t>
+          <t>2970; 13038</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9852; 24417</t>
+          <t>10167; 24763</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11015; 26829</t>
+          <t>10297; 26956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13109; 31407</t>
+          <t>13524; 31747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12541; 28938</t>
+          <t>12413; 28651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17693; 38944</t>
+          <t>18070; 39345</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>773; 7086</t>
+          <t>816; 7147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1957; 10388</t>
+          <t>1917; 10159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6628</t>
+          <t>0; 6218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7335</t>
+          <t>0; 5680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>874; 7990</t>
+          <t>866; 7365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5970</t>
+          <t>0; 5796</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4562; 12668</t>
+          <t>4787; 12897</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>942; 8646</t>
+          <t>930; 8904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3641; 14007</t>
+          <t>3706; 15001</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>927; 8165</t>
+          <t>969; 9145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5555; 15601</t>
+          <t>5456; 15993</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10210; 25289</t>
+          <t>10013; 24879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15699; 34373</t>
+          <t>15486; 35227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16796; 35432</t>
+          <t>16687; 33490</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10399; 27848</t>
+          <t>9762; 27574</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6496; 21166</t>
+          <t>6823; 20507</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13931; 32991</t>
+          <t>13536; 31420</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11817; 28885</t>
+          <t>12618; 29936</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31210; 50503</t>
+          <t>31068; 50434</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19934; 40590</t>
+          <t>19210; 40138</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33356; 60678</t>
+          <t>32712; 59959</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33048; 56775</t>
+          <t>32494; 57522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45465; 71921</t>
+          <t>45280; 71441</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$consultar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 31,65</t>
+          <t>3,67; 31,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 18,62</t>
+          <t>3,22; 18,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 35,35</t>
+          <t>11,91; 34,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 27,66</t>
+          <t>6,97; 26,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 21,88</t>
+          <t>2,7; 22,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 14,54</t>
+          <t>4,41; 14,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 24,18</t>
+          <t>6,84; 23,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 26,7</t>
+          <t>13,08; 25,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 19,5</t>
+          <t>4,77; 20,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,41</t>
+          <t>4,89; 13,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 25,07</t>
+          <t>11,48; 24,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 24,26</t>
+          <t>13,06; 23,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 23,46</t>
+          <t>7,24; 24,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,79</t>
+          <t>3,1; 10,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 16,82</t>
+          <t>6,07; 17,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 15,96</t>
+          <t>3,39; 14,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 37,56</t>
+          <t>8,58; 34,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 15,34</t>
+          <t>4,43; 15,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 15,4</t>
+          <t>3,61; 16,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 24,29</t>
+          <t>9,5; 22,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 23,74</t>
+          <t>9,69; 23,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,74</t>
+          <t>4,31; 10,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,92</t>
+          <t>5,93; 14,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,96</t>
+          <t>7,36; 16,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 36,84</t>
+          <t>4,22; 35,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 38,99</t>
+          <t>7,15; 39,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 19,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,1</t>
+          <t>0,0; 15,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,08</t>
+          <t>0,0; 30,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 25,6</t>
+          <t>2,91; 25,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,69</t>
+          <t>0,0; 18,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 41,78</t>
+          <t>15,56; 41,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 27,28</t>
+          <t>2,81; 26,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 27,36</t>
+          <t>7,02; 26,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,8</t>
+          <t>1,53; 14,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 24,95</t>
+          <t>8,87; 24,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,21</t>
+          <t>7,87; 20,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 12,45</t>
+          <t>5,21; 11,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,94</t>
+          <t>8,71; 17,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,87</t>
+          <t>5,05; 13,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,86</t>
+          <t>6,55; 21,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,35</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,73</t>
+          <t>6,09; 15,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 23,75</t>
+          <t>14,16; 23,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,51</t>
+          <t>8,81; 17,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,16</t>
+          <t>6,22; 11,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 14,83</t>
+          <t>8,76; 14,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 17,37</t>
+          <t>10,94; 16,81</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>21959</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>888; 7969</t>
+          <t>925; 7810</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2987; 13926</t>
+          <t>2406; 13578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5467; 16158</t>
+          <t>5442; 15662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2588; 9847</t>
+          <t>2639; 10192</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1182; 9960</t>
+          <t>1228; 10228</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4982; 16267</t>
+          <t>4930; 15948</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5274; 18041</t>
+          <t>5104; 17359</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10922; 21241</t>
+          <t>11055; 21804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3159; 13785</t>
+          <t>3372; 14599</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9538; 25036</t>
+          <t>9128; 24913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13092; 30159</t>
+          <t>13810; 29339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14679; 27939</t>
+          <t>15975; 28802</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>27479</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5465; 18420</t>
+          <t>5684; 19113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5870; 19641</t>
+          <t>5643; 19884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6752; 20378</t>
+          <t>7352; 20992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4885; 20752</t>
+          <t>4755; 20780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2970; 13163</t>
+          <t>3007; 12238</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4793; 17446</t>
+          <t>5038; 17724</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2970; 13038</t>
+          <t>3054; 13999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10167; 24763</t>
+          <t>10547; 25464</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10297; 26956</t>
+          <t>11001; 26324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13524; 31747</t>
+          <t>12746; 31926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12413; 28651</t>
+          <t>12214; 29820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18070; 39345</t>
+          <t>18482; 40566</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>11663</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>816; 7147</t>
+          <t>819; 6947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1917; 10159</t>
+          <t>1864; 10266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6218</t>
+          <t>0; 6117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5680</t>
+          <t>0; 6505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>866; 7365</t>
+          <t>838; 7348</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5796</t>
+          <t>0; 5772</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4787; 12897</t>
+          <t>5484; 14588</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930; 8904</t>
+          <t>916; 8668</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3706; 15001</t>
+          <t>3850; 14301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>969; 9145</t>
+          <t>945; 8790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5456; 15993</t>
+          <t>6822; 19023</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10013; 24879</t>
+          <t>9685; 25623</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15486; 35227</t>
+          <t>14742; 33540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16687; 33490</t>
+          <t>17227; 34455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9762; 27574</t>
+          <t>11101; 30208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6823; 20507</t>
+          <t>6149; 20042</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13536; 31420</t>
+          <t>13971; 31828</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12618; 29936</t>
+          <t>11592; 29343</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31068; 50434</t>
+          <t>32670; 53996</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19210; 40138</t>
+          <t>19114; 38341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32712; 59959</t>
+          <t>33435; 59969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32494; 57522</t>
+          <t>34001; 57094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45280; 71441</t>
+          <t>49288; 75739</t>
         </is>
       </c>
     </row>
